--- a/docs/legal-acts/export/EU 2024-1183.xlsx
+++ b/docs/legal-acts/export/EU 2024-1183.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
